--- a/public/static/template/import_khach_hang.xlsx
+++ b/public/static/template/import_khach_hang.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10514"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thanhcong/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac24h/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAAA1DA3-F164-8943-A07C-6E1AF9F58836}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C4F4523-206A-7940-8CB6-87B5182A0264}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="460" windowWidth="28800" windowHeight="15840" xr2:uid="{EC5AED34-FE60-C04F-A99D-FEA9725203CD}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="28800" windowHeight="15840" xr2:uid="{EC5AED34-FE60-C04F-A99D-FEA9725203CD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,10 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
-  <si>
-    <t>Tên phụ huynh</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Số điện thoại</t>
   </si>
@@ -45,36 +42,12 @@
     <t>Người phụ trách</t>
   </si>
   <si>
-    <t>Học sinh 1</t>
-  </si>
-  <si>
-    <t>Ngày sinh học sinh 1</t>
-  </si>
-  <si>
-    <t>Học sinh 2</t>
-  </si>
-  <si>
-    <t>Ngày sinh học sinh 2</t>
-  </si>
-  <si>
-    <t>Số điện thoại 2</t>
-  </si>
-  <si>
-    <t>Trung tâm checkin</t>
-  </si>
-  <si>
-    <t>Thời gian checkin</t>
-  </si>
-  <si>
     <t>Nguyễn Thị Huế</t>
   </si>
   <si>
     <t>0954112541</t>
   </si>
   <si>
-    <t>0954112542</t>
-  </si>
-  <si>
     <t>demo@gmail.com</t>
   </si>
   <si>
@@ -87,22 +60,13 @@
     <t>C00001</t>
   </si>
   <si>
-    <t>Nguyễn Văn A</t>
-  </si>
-  <si>
-    <t>2015-07-08</t>
-  </si>
-  <si>
-    <t>2016-08-16</t>
-  </si>
-  <si>
-    <t>Nguyễn Văn B</t>
-  </si>
-  <si>
-    <t>C01</t>
-  </si>
-  <si>
-    <t>2022-07-24</t>
+    <t>Họ tên</t>
+  </si>
+  <si>
+    <t>Link facebook</t>
+  </si>
+  <si>
+    <t>https://lapo.edu.vn/ket-qua-hoc-vien/</t>
   </si>
 </sst>
 </file>
@@ -497,8 +461,8 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.1640625" customWidth="1"/>
-    <col min="2" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="24.5" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="4" width="24.5" customWidth="1"/>
     <col min="5" max="5" width="26.1640625" customWidth="1"/>
     <col min="6" max="6" width="18.83203125" customWidth="1"/>
     <col min="7" max="7" width="20.6640625" customWidth="1"/>
@@ -512,91 +476,60 @@
   <sheetData>
     <row r="1" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>10</v>
-      </c>
       <c r="D1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>4</v>
-      </c>
-      <c r="G1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>16</v>
-      </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>25</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="M2" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" xr:uid="{413A1DC1-E90E-B242-8B78-513C45E2C343}"/>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{413A1DC1-E90E-B242-8B78-513C45E2C343}"/>
+    <hyperlink ref="D2" r:id="rId2" xr:uid="{346E8B15-5C9E-EB44-9348-EB754B3489CE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>